--- a/stories/arbres/TREE-LAN-006.xlsx
+++ b/stories/arbres/TREE-LAN-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé marche à la ferme avec papa. Un bruit arrive. Papa dit : c'est un son. Quel nom ? Zoé écoute. Elle va dire le nom. Son, puis nom.</t>
+          <t>Zoé marche à la ferme avec papa. Un bruit arrive. C'est un son. Quel nom ? Zoé écoute. Elle va dire le nom. Son, puis nom.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé marche à la ferme avec papa. Un bruit arrive.
+papa|C'est un son. Quel nom ?
+narrateur|Zoé écoute. Elle va dire le nom. Son, puis nom.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cour, l'étable, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dans la cour, un son : meuh. Papa dit : quel nom ? Zoé dit : la vache. C'est un son. Elle dit le nom.</t>
+          <t>Dans la cour, un son : meuh. Quel nom ? La vache. C'est un son. Elle dit le nom.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la cour, un son : meuh.
+papa|Quel nom ?
+enfant-f|La vache. C'est un son. Elle dit le nom.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la cour, Zoé entend. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a entendu un son. Elle a dit le nom.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2225,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la vache, la poule, ou l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2203,7 +2254,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>La vache mugit. Zoé dit : c'est un son. Le nom, c'est la vache.</t>
+          <t>La vache mugit. C'est un son. Le nom, c'est la vache.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2341,6 +2392,13 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|La vache mugit.
+enfant-f|C'est un son.
+narrateur|Le nom, c'est la vache.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend meuh à la cour. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend cot cot à la cour. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend plic ploc à la cour. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3754,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|La poule chante. Un son. Zoé dit le nom : la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3945,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4112,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend meuh à la cour. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4279,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4446,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend cot cot à la cour. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4613,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4780,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend plic ploc à la cour. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4947,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5114,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|L'eau de l'auge cloche. Un son. Zoé dit le nom : l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5305,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5472,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend meuh à la cour. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5639,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5806,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend cot cot à la cour. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5973,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6140,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend plic ploc à la cour. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6307,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6474,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Dans l'étable, un son : cot cot. Zoé dit le nom : la poule. Un son. Un nom.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6655,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Dans l'étable, Zoé entend. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6828,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Un son. On dit le nom.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6833,6 +7021,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la vache, la poule, ou l'eau.</t>
         </is>
       </c>
     </row>
@@ -6997,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Dans l'étable, la vache. Un son. Zoé dit le nom.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7345,6 +7548,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend meuh à l'étable. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend cot cot à l'étable. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend plic ploc à l'étable. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|La poule picore. Un son. Zoé nomme : la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend meuh à l'étable. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend cot cot à l'étable. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend plic ploc à l'étable. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|L'eau tombe. Un son. Zoé dit le nom : l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9985,6 +10268,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend meuh à l'étable. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10435,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10602,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend cot cot à l'étable. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10769,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10936,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend plic ploc à l'étable. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11103,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11270,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, l'eau cloche. Un son. Zoé dit le nom : l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11451,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, Zoé entend. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11624,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé nomme le son. Vache, poule ou eau.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11489,6 +11817,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la vache, la poule, ou l'eau.</t>
         </is>
       </c>
     </row>
@@ -11653,6 +11986,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, la vache au loin. Un son. Zoé dit le nom.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11839,6 +12177,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12001,6 +12344,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend meuh à le jardin. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12163,6 +12511,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12325,6 +12678,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend cot cot à le jardin. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12487,6 +12845,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12649,6 +13012,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend plic ploc à le jardin. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12811,6 +13179,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12973,6 +13346,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Une poule passe. Un son. Zoé nomme la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13159,6 +13537,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13321,6 +13704,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend meuh à le jardin. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13483,6 +13871,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13645,6 +14038,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend cot cot à le jardin. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13807,6 +14205,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13969,6 +14372,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend plic ploc à le jardin. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14131,6 +14539,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14293,6 +14706,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Le robinet du jardin. Un son. Zoé dit le nom : l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14479,6 +14897,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14641,6 +15064,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend meuh à le jardin. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14803,6 +15231,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14965,6 +15398,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend cot cot à le jardin. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15127,6 +15565,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15289,6 +15732,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend plic ploc à le jardin. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15451,6 +15899,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15469,7 +15922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15493,6 +15946,13 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-LAN-006.xlsx
+++ b/stories/arbres/TREE-LAN-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Zoé écoute. Elle va dire le nom. Son, puis nom.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre la cour, l'étable, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 enfant-f|La vache. C'est un son. Elle dit le nom.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Dans la cour, Zoé entend. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Zoé a entendu un son. Elle a dit le nom.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre la vache, la poule, ou l'eau.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
 narrateur|Le nom, c'est la vache.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Zoé entend meuh à la cour. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Zoé entend cot cot à la cour. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,7 @@
           <t>narrateur|Zoé entend plic ploc à la cour. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3778,7 @@
           <t>narrateur|La poule chante. Un son. Zoé dit le nom : la poule.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +3970,7 @@
           <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4117,6 +4138,7 @@
           <t>narrateur|Zoé entend meuh à la cour. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4284,6 +4306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4451,6 +4474,7 @@
           <t>narrateur|Zoé entend cot cot à la cour. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4618,6 +4642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4785,6 +4810,7 @@
           <t>narrateur|Zoé entend plic ploc à la cour. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4952,6 +4978,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5119,6 +5146,7 @@
           <t>narrateur|L'eau de l'auge cloche. Un son. Zoé dit le nom : l'eau.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5310,6 +5338,7 @@
           <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5477,6 +5506,7 @@
           <t>narrateur|Zoé entend meuh à la cour. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5644,6 +5674,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5811,6 +5842,7 @@
           <t>narrateur|Zoé entend cot cot à la cour. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5978,6 +6010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6145,6 +6178,7 @@
           <t>narrateur|Zoé entend plic ploc à la cour. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6312,6 +6346,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
           <t>narrateur|Dans l'étable, un son : cot cot. Zoé dit le nom : la poule. Un son. Un nom.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6662,6 +6698,7 @@
           <t>narrateur|Dans l'étable, Zoé entend. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6833,6 +6870,7 @@
           <t>narrateur|Oui. Un son. On dit le nom.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre la vache, la poule, ou l'eau.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Dans l'étable, la vache. Un son. Zoé dit le nom.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Zoé entend meuh à l'étable. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Zoé entend cot cot à l'étable. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Zoé entend plic ploc à l'étable. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|La poule picore. Un son. Zoé nomme : la poule.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Zoé entend meuh à l'étable. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Zoé entend cot cot à l'étable. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Zoé entend plic ploc à l'étable. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|L'eau tombe. Un son. Zoé dit le nom : l'eau.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|Zoé entend meuh à l'étable. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|Zoé entend cot cot à l'étable. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|Zoé entend plic ploc à l'étable. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11275,6 +11338,7 @@
           <t>narrateur|Au jardin, l'eau cloche. Un son. Zoé dit le nom : l'eau.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11458,6 +11522,7 @@
           <t>narrateur|Au jardin, Zoé entend. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11629,6 +11694,7 @@
           <t>narrateur|Zoé nomme le son. Vache, poule ou eau.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11824,6 +11890,7 @@
           <t>narrateur|On peut prendre la vache, la poule, ou l'eau.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11991,6 +12058,7 @@
           <t>narrateur|Au jardin, la vache au loin. Un son. Zoé dit le nom.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12182,6 +12250,7 @@
           <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12349,6 +12418,7 @@
           <t>narrateur|Zoé entend meuh à le jardin. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12516,6 +12586,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12683,6 +12754,7 @@
           <t>narrateur|Zoé entend cot cot à le jardin. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12850,6 +12922,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13017,6 +13090,7 @@
           <t>narrateur|Zoé entend plic ploc à le jardin. C'est un son. Elle dit le nom : la vache. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13184,6 +13258,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13351,6 +13426,7 @@
           <t>narrateur|Une poule passe. Un son. Zoé nomme la poule.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13542,6 +13618,7 @@
           <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13709,6 +13786,7 @@
           <t>narrateur|Zoé entend meuh à le jardin. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13876,6 +13954,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14043,6 +14122,7 @@
           <t>narrateur|Zoé entend cot cot à le jardin. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14210,6 +14290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14377,6 +14458,7 @@
           <t>narrateur|Zoé entend plic ploc à le jardin. C'est un son. Elle dit le nom : la poule. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14544,6 +14626,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14711,6 +14794,7 @@
           <t>narrateur|Le robinet du jardin. Un son. Zoé dit le nom : l'eau.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14902,6 +14986,7 @@
           <t>narrateur|On peut prendre meuh, cot cot, ou plic ploc.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15069,6 +15154,7 @@
           <t>narrateur|Zoé entend meuh à le jardin. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15236,6 +15322,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15403,6 +15490,7 @@
           <t>narrateur|Zoé entend cot cot à le jardin. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15570,6 +15658,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15737,6 +15826,7 @@
           <t>narrateur|Zoé entend plic ploc à le jardin. C'est un son. Elle dit le nom : l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15904,6 +15994,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15922,7 +16013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15953,6 +16044,20 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15967,7 +16072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16154,6 +16259,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
